--- a/data/classData.xlsx
+++ b/data/classData.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>subject_code</t>
   </si>
@@ -88,6 +88,9 @@
     <t>password (mặc định)</t>
   </si>
   <si>
+    <t>role</t>
+  </si>
+  <si>
     <t>Nguyễn Văn A</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
   </si>
   <si>
     <t>Huce@123</t>
+  </si>
+  <si>
+    <t>student</t>
   </si>
   <si>
     <t>Trần Thị B</t>
@@ -125,10 +131,18 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -618,141 +632,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -768,7 +783,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1098,59 +1113,59 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" ht="27.15" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="40.35" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="40.35" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="27.15" spans="1:2">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="27.15" spans="1:3">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="14.55" spans="1:2">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="14.55" spans="1:3">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="27.15" spans="1:2">
-      <c r="A6" s="2" t="s">
+    <row r="6" ht="27.15" spans="1:3">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1164,13 +1179,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.66666666666667"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="19.1" customWidth="1"/>
+    <col min="3" max="3" width="11.4" customWidth="1"/>
+    <col min="4" max="4" width="17.9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1183,47 +1201,59 @@
       <c r="D1" t="s">
         <v>18</v>
       </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>20210001</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>20210002</v>
       </c>
       <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
+      <c r="E3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>20210003</v>
       </c>
       <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1247,31 +1277,31 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
